--- a/backend/media/templates/monthly_sales_commission.xlsx
+++ b/backend/media/templates/monthly_sales_commission.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,12 +46,6 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
       <sz val="11"/>
     </font>
     <font>
@@ -157,10 +151,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -529,10 +523,10 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -542,7 +536,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INTERNAL FINANCE TRAINING: VEHICLE PRICE CATALOG</t>
+          <t>INTERNAL FINANCE TRAINING: VEHICLE MASTER CATALOG</t>
         </is>
       </c>
     </row>
@@ -671,25 +665,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INTERNAL FINANCE TRAINING: MONTHLY SALES COMMISSION LEDGER</t>
+          <t>INTERNAL FINANCE TRAINING: MONTHLY SALES COMMISSION AUDIT</t>
         </is>
       </c>
     </row>
@@ -704,7 +698,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sale ID</t>
+          <t>Deal ID</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -729,12 +723,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Commission Rate</t>
+          <t>Comm Rate</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Commission Amount</t>
+          <t>Comm Amount</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -744,10 +738,8 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>S1001</t>
-        </is>
+      <c r="A5" s="5" t="n">
+        <v>1001</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -772,17 +764,15 @@
           <t>Dubai</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>Branch Sales Summaries</t>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Audited Metrics:</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>S1002</t>
-        </is>
+      <c r="A6" s="7" t="n">
+        <v>1002</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
@@ -807,18 +797,16 @@
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="n"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Dubai Total Sales (AED):</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>S1003</t>
-        </is>
+      <c r="A7" s="5" t="n">
+        <v>1003</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -845,10 +833,8 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>S1004</t>
-        </is>
+      <c r="A8" s="7" t="n">
+        <v>1004</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -873,17 +859,15 @@
           <t>Sharjah</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>Formulas Required:</t>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>Required formulas:</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>S1005</t>
-        </is>
+      <c r="A9" s="5" t="n">
+        <v>1005</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -905,20 +889,18 @@
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>E5:E10: lookup Price based on VIN Prefix from VehicleCatalog sheet (use VLOOKUP)</t>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>E5-E10: Lookup Price from Catalog (VLOOKUP)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>S1006</t>
-        </is>
+      <c r="A10" s="7" t="n">
+        <v>1006</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -940,26 +922,26 @@
       <c r="G10" s="8" t="inlineStr"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>F5:F10: Comm Rate. 5% (0.05) if Model is 'Land Cruiser', else 3% (0.03) (use IF)</t>
+          <t>Sharjah</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>F5-F10: Rate: 5% for LC, 3% for others (IF)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>G5:G10: Commission Amount = Price * Comm Rate</t>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>G5-G10: Commission Amount = Price * Rate</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>K6: Dubai Total Sales from Price column (use SUMIFS)</t>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>J6: Total Sales Generated by Dubai (SUMIFS)</t>
         </is>
       </c>
     </row>
